--- a/public/reports/weekly_briefing/2026-09-07.xlsx
+++ b/public/reports/weekly_briefing/2026-09-07.xlsx
@@ -14,7 +14,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'신고가 근접'!$A$5:$L$26</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'섹터x수급'!$A$4:$N$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'섹터x수급'!$A$4:$O$28</definedName>
   </definedNames>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
@@ -27,7 +27,7 @@
     <numFmt numFmtId="165" formatCode="+0;-0;0"/>
     <numFmt numFmtId="166" formatCode="+#,##0;-#,##0;0"/>
     <numFmt numFmtId="167" formatCode="+#,##0.0;-#,##0.0;0.0"/>
-    <numFmt numFmtId="168" formatCode="+0.0;-0.0;0.0"/>
+    <numFmt numFmtId="168" formatCode="+0.00;-0.00;0"/>
     <numFmt numFmtId="169" formatCode="#,##0.0"/>
     <numFmt numFmtId="170" formatCode="+0.00;-0.00;0.00"/>
   </numFmts>
@@ -532,6 +532,9 @@
     <xf numFmtId="166" fontId="23" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="166" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="170" fontId="24" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -540,9 +543,6 @@
     </xf>
     <xf numFmtId="0" fontId="26" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -947,7 +947,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:K158"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.9" customWidth="1" style="15" min="1" max="1"/>
     <col width="14.9" customWidth="1" style="15" min="2" max="2"/>
@@ -2327,10 +2327,10 @@
         <v>9480.299999999999</v>
       </c>
       <c r="J54" s="31" t="n">
-        <v>235789.8</v>
+        <v>231378.1</v>
       </c>
       <c r="K54" s="31" t="n">
-        <v>-11657.4</v>
+        <v>-16069.1</v>
       </c>
     </row>
     <row r="55">
@@ -2368,10 +2368,10 @@
         <v>1185</v>
       </c>
       <c r="J55" s="31" t="n">
-        <v>30216.4</v>
+        <v>29118.3</v>
       </c>
       <c r="K55" s="31" t="n">
-        <v>-2595.6</v>
+        <v>-3693.7</v>
       </c>
     </row>
     <row r="56">
@@ -2409,10 +2409,10 @@
         <v>18729.6</v>
       </c>
       <c r="J56" s="31" t="n">
-        <v>227552.2</v>
+        <v>220014.1</v>
       </c>
       <c r="K56" s="31" t="n">
-        <v>1747.9</v>
+        <v>-5790.2</v>
       </c>
     </row>
     <row r="57">
@@ -2450,10 +2450,10 @@
         <v>2281.2</v>
       </c>
       <c r="J57" s="31" t="n">
-        <v>19559.4</v>
+        <v>19863</v>
       </c>
       <c r="K57" s="31" t="n">
-        <v>83.90000000000001</v>
+        <v>387.5</v>
       </c>
     </row>
     <row r="58">
@@ -2491,10 +2491,10 @@
         <v>414.3</v>
       </c>
       <c r="J58" s="31" t="n">
-        <v>3684.3</v>
+        <v>3487.9</v>
       </c>
       <c r="K58" s="31" t="n">
-        <v>158.5</v>
+        <v>-37.9</v>
       </c>
     </row>
     <row r="59">
@@ -2532,10 +2532,10 @@
         <v>1349.4</v>
       </c>
       <c r="J59" s="31" t="n">
-        <v>16196</v>
+        <v>15397.8</v>
       </c>
       <c r="K59" s="31" t="n">
-        <v>788.7</v>
+        <v>-9.5</v>
       </c>
     </row>
     <row r="60">
@@ -2573,10 +2573,10 @@
         <v>188.1</v>
       </c>
       <c r="J60" s="31" t="n">
-        <v>9451.700000000001</v>
+        <v>9268.299999999999</v>
       </c>
       <c r="K60" s="31" t="n">
-        <v>347.2</v>
+        <v>163.8</v>
       </c>
     </row>
     <row r="61">
@@ -2614,10 +2614,10 @@
         <v>654.6</v>
       </c>
       <c r="J61" s="31" t="n">
-        <v>7607.6</v>
+        <v>6860.5</v>
       </c>
       <c r="K61" s="31" t="n">
-        <v>982.5</v>
+        <v>235.4</v>
       </c>
     </row>
     <row r="62">
@@ -2696,10 +2696,10 @@
         <v>629.1</v>
       </c>
       <c r="J63" s="31" t="n">
-        <v>8881.5</v>
+        <v>8965</v>
       </c>
       <c r="K63" s="31" t="n">
-        <v>412.9</v>
+        <v>496.4</v>
       </c>
     </row>
     <row r="64">
@@ -2737,10 +2737,10 @@
         <v>1713.4</v>
       </c>
       <c r="J64" s="31" t="n">
-        <v>33399</v>
+        <v>33246</v>
       </c>
       <c r="K64" s="31" t="n">
-        <v>-5411</v>
+        <v>-5564</v>
       </c>
     </row>
     <row r="65">
@@ -2778,10 +2778,10 @@
         <v>381.5</v>
       </c>
       <c r="J65" s="31" t="n">
-        <v>12108.8</v>
+        <v>11912</v>
       </c>
       <c r="K65" s="31" t="n">
-        <v>-721.5</v>
+        <v>-918.3</v>
       </c>
     </row>
     <row r="66">
@@ -2860,10 +2860,10 @@
         <v>815.7</v>
       </c>
       <c r="J67" s="31" t="n">
-        <v>13708</v>
+        <v>13358.1</v>
       </c>
       <c r="K67" s="31" t="n">
-        <v>180.1</v>
+        <v>-169.8</v>
       </c>
     </row>
     <row r="68">
@@ -2901,10 +2901,10 @@
         <v>979.5</v>
       </c>
       <c r="J68" s="31" t="n">
-        <v>11204.9</v>
+        <v>11076.1</v>
       </c>
       <c r="K68" s="31" t="n">
-        <v>-877.2</v>
+        <v>-1006</v>
       </c>
     </row>
     <row r="69">
@@ -2942,10 +2942,10 @@
         <v>301.6</v>
       </c>
       <c r="J69" s="31" t="n">
-        <v>14324.8</v>
+        <v>14373.7</v>
       </c>
       <c r="K69" s="31" t="n">
-        <v>-570.1</v>
+        <v>-521.2</v>
       </c>
     </row>
     <row r="70">
@@ -3024,10 +3024,10 @@
         <v>647.1</v>
       </c>
       <c r="J71" s="31" t="n">
-        <v>31440</v>
+        <v>31851.3</v>
       </c>
       <c r="K71" s="31" t="n">
-        <v>-1186.9</v>
+        <v>-775.6</v>
       </c>
     </row>
     <row r="72">
@@ -3065,10 +3065,10 @@
         <v>1135.1</v>
       </c>
       <c r="J72" s="31" t="n">
-        <v>13553.1</v>
+        <v>13097</v>
       </c>
       <c r="K72" s="31" t="n">
-        <v>-940.3</v>
+        <v>-1396.4</v>
       </c>
     </row>
     <row r="73">
@@ -3106,10 +3106,10 @@
         <v>1461.6</v>
       </c>
       <c r="J73" s="31" t="n">
-        <v>32699.9</v>
+        <v>30926.8</v>
       </c>
       <c r="K73" s="31" t="n">
-        <v>-741.8</v>
+        <v>-2514.9</v>
       </c>
     </row>
     <row r="74"/>
@@ -5136,7 +5136,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L28"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18.5" customWidth="1" style="15" min="1" max="1"/>
     <col width="9" customWidth="1" style="15" min="2" max="2"/>
@@ -6211,8 +6211,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q59"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <dimension ref="A1:Q73"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4.5" customWidth="1" style="15" min="1" max="1"/>
     <col width="18" customWidth="1" style="15" min="2" max="2"/>
@@ -8625,7 +8625,7 @@
       </c>
       <c r="J45" s="25" t="inlineStr">
         <is>
-          <t>F8 보험</t>
+          <t>F8 기타법인</t>
         </is>
       </c>
       <c r="N45" s="58" t="inlineStr">
@@ -8738,7 +8738,7 @@
         </is>
       </c>
     </row>
-    <row r="48">
+    <row r="48" ht="31" customHeight="1" s="15">
       <c r="A48" s="30" t="n">
         <v>1</v>
       </c>
@@ -8776,32 +8776,32 @@
       </c>
       <c r="K48" s="31" t="inlineStr">
         <is>
-          <t>SK스퀘어</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="L48" s="35" t="inlineStr">
         <is>
-          <t>금융</t>
+          <t>전기·전자</t>
         </is>
       </c>
       <c r="M48" s="47" t="n">
-        <v>248</v>
+        <v>56704</v>
       </c>
       <c r="N48" s="30" t="n">
         <v>1</v>
       </c>
       <c r="O48" s="31" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
-        </is>
-      </c>
-      <c r="P48" s="35" t="inlineStr">
-        <is>
-          <t>전기·전자</t>
+          <t>현대차</t>
+        </is>
+      </c>
+      <c r="P48" s="62" t="inlineStr">
+        <is>
+          <t>운송장비·부품</t>
         </is>
       </c>
       <c r="Q48" s="61" t="n">
-        <v>-311</v>
+        <v>-161</v>
       </c>
     </row>
     <row r="49" ht="31" customHeight="1" s="15">
@@ -8842,7 +8842,7 @@
       </c>
       <c r="K49" s="31" t="inlineStr">
         <is>
-          <t>삼성전자우</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="L49" s="35" t="inlineStr">
@@ -8851,23 +8851,23 @@
         </is>
       </c>
       <c r="M49" s="47" t="n">
-        <v>200</v>
+        <v>25969</v>
       </c>
       <c r="N49" s="30" t="n">
         <v>2</v>
       </c>
       <c r="O49" s="31" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>LG에너지솔루션</t>
         </is>
       </c>
       <c r="P49" s="35" t="inlineStr">
         <is>
-          <t>금융</t>
+          <t>전기·전자</t>
         </is>
       </c>
       <c r="Q49" s="61" t="n">
-        <v>-74</v>
+        <v>-137</v>
       </c>
     </row>
     <row r="50" ht="31" customHeight="1" s="15">
@@ -8908,32 +8908,32 @@
       </c>
       <c r="K50" s="31" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>셀트리온</t>
         </is>
       </c>
       <c r="L50" s="35" t="inlineStr">
         <is>
-          <t>전기·전자</t>
+          <t>제약</t>
         </is>
       </c>
       <c r="M50" s="47" t="n">
-        <v>130</v>
+        <v>484</v>
       </c>
       <c r="N50" s="30" t="n">
         <v>3</v>
       </c>
       <c r="O50" s="31" t="inlineStr">
         <is>
-          <t>셀트리온</t>
+          <t>HD현대</t>
         </is>
       </c>
       <c r="P50" s="35" t="inlineStr">
         <is>
-          <t>제약</t>
+          <t>금융</t>
         </is>
       </c>
       <c r="Q50" s="61" t="n">
-        <v>-66</v>
+        <v>-103</v>
       </c>
     </row>
     <row r="51" ht="31" customHeight="1" s="15">
@@ -8974,35 +8974,35 @@
       </c>
       <c r="K51" s="31" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>LG</t>
         </is>
       </c>
       <c r="L51" s="35" t="inlineStr">
         <is>
-          <t>기계·장비</t>
+          <t>금융</t>
         </is>
       </c>
       <c r="M51" s="47" t="n">
-        <v>98</v>
+        <v>298</v>
       </c>
       <c r="N51" s="30" t="n">
         <v>4</v>
       </c>
       <c r="O51" s="31" t="inlineStr">
         <is>
-          <t>NAVER</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="P51" s="35" t="inlineStr">
         <is>
-          <t>IT 서비스</t>
+          <t>일반서비스</t>
         </is>
       </c>
       <c r="Q51" s="61" t="n">
-        <v>-61</v>
-      </c>
-    </row>
-    <row r="52" ht="31" customHeight="1" s="15">
+        <v>-85</v>
+      </c>
+    </row>
+    <row r="52">
       <c r="A52" s="30" t="n">
         <v>5</v>
       </c>
@@ -9040,32 +9040,32 @@
       </c>
       <c r="K52" s="31" t="inlineStr">
         <is>
-          <t>HD현대중공업</t>
-        </is>
-      </c>
-      <c r="L52" s="62" t="inlineStr">
-        <is>
-          <t>운송장비·부품</t>
+          <t>현대제철</t>
+        </is>
+      </c>
+      <c r="L52" s="35" t="inlineStr">
+        <is>
+          <t>금속</t>
         </is>
       </c>
       <c r="M52" s="47" t="n">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="N52" s="30" t="n">
         <v>5</v>
       </c>
       <c r="O52" s="31" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>SK스퀘어</t>
         </is>
       </c>
       <c r="P52" s="35" t="inlineStr">
         <is>
-          <t>일반서비스</t>
+          <t>금융</t>
         </is>
       </c>
       <c r="Q52" s="61" t="n">
-        <v>-60</v>
+        <v>-69</v>
       </c>
     </row>
     <row r="53">
@@ -9106,32 +9106,32 @@
       </c>
       <c r="K53" s="31" t="inlineStr">
         <is>
-          <t>두산</t>
+          <t>DL이앤씨</t>
         </is>
       </c>
       <c r="L53" s="35" t="inlineStr">
         <is>
-          <t>전기·전자</t>
+          <t>건설</t>
         </is>
       </c>
       <c r="M53" s="47" t="n">
-        <v>68</v>
+        <v>99</v>
       </c>
       <c r="N53" s="30" t="n">
         <v>6</v>
       </c>
       <c r="O53" s="31" t="inlineStr">
         <is>
-          <t>에이피알</t>
+          <t>KB금융</t>
         </is>
       </c>
       <c r="P53" s="35" t="inlineStr">
         <is>
-          <t>화학</t>
+          <t>금융</t>
         </is>
       </c>
       <c r="Q53" s="61" t="n">
-        <v>-57</v>
+        <v>-42</v>
       </c>
     </row>
     <row r="54">
@@ -9172,23 +9172,23 @@
       </c>
       <c r="K54" s="31" t="inlineStr">
         <is>
-          <t>현대건설</t>
+          <t>삼성SDI</t>
         </is>
       </c>
       <c r="L54" s="35" t="inlineStr">
         <is>
-          <t>건설</t>
+          <t>전기·전자</t>
         </is>
       </c>
       <c r="M54" s="47" t="n">
-        <v>56</v>
+        <v>85</v>
       </c>
       <c r="N54" s="30" t="n">
         <v>7</v>
       </c>
       <c r="O54" s="31" t="inlineStr">
         <is>
-          <t>HD현대일렉트릭</t>
+          <t>삼성전기</t>
         </is>
       </c>
       <c r="P54" s="35" t="inlineStr">
@@ -9197,10 +9197,10 @@
         </is>
       </c>
       <c r="Q54" s="61" t="n">
-        <v>-57</v>
-      </c>
-    </row>
-    <row r="55" ht="31" customHeight="1" s="15">
+        <v>-41</v>
+      </c>
+    </row>
+    <row r="55">
       <c r="A55" s="30" t="n">
         <v>8</v>
       </c>
@@ -9238,7 +9238,7 @@
       </c>
       <c r="K55" s="31" t="inlineStr">
         <is>
-          <t>DB하이텍</t>
+          <t>두산</t>
         </is>
       </c>
       <c r="L55" s="35" t="inlineStr">
@@ -9247,23 +9247,23 @@
         </is>
       </c>
       <c r="M55" s="47" t="n">
-        <v>44</v>
+        <v>79</v>
       </c>
       <c r="N55" s="30" t="n">
         <v>8</v>
       </c>
       <c r="O55" s="31" t="inlineStr">
         <is>
-          <t>현대모비스</t>
-        </is>
-      </c>
-      <c r="P55" s="62" t="inlineStr">
-        <is>
-          <t>운송장비·부품</t>
+          <t>HPSP</t>
+        </is>
+      </c>
+      <c r="P55" s="35" t="inlineStr">
+        <is>
+          <t>기계·장비</t>
         </is>
       </c>
       <c r="Q55" s="61" t="n">
-        <v>-50</v>
+        <v>-40</v>
       </c>
     </row>
     <row r="56">
@@ -9304,32 +9304,32 @@
       </c>
       <c r="K56" s="31" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>현대백화점</t>
         </is>
       </c>
       <c r="L56" s="35" t="inlineStr">
         <is>
-          <t>건설</t>
+          <t>유통</t>
         </is>
       </c>
       <c r="M56" s="47" t="n">
-        <v>38</v>
+        <v>70</v>
       </c>
       <c r="N56" s="30" t="n">
         <v>9</v>
       </c>
       <c r="O56" s="31" t="inlineStr">
         <is>
-          <t>삼양식품</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="P56" s="35" t="inlineStr">
         <is>
-          <t>음식료·담배</t>
+          <t>운송·창고</t>
         </is>
       </c>
       <c r="Q56" s="61" t="n">
-        <v>-42</v>
+        <v>-40</v>
       </c>
     </row>
     <row r="57">
@@ -9370,44 +9370,451 @@
       </c>
       <c r="K57" s="31" t="inlineStr">
         <is>
-          <t>삼성물산</t>
+          <t>삼성전자우</t>
         </is>
       </c>
       <c r="L57" s="35" t="inlineStr">
         <is>
-          <t>유통</t>
+          <t>전기·전자</t>
         </is>
       </c>
       <c r="M57" s="47" t="n">
-        <v>33</v>
+        <v>62</v>
       </c>
       <c r="N57" s="30" t="n">
         <v>10</v>
       </c>
       <c r="O57" s="31" t="inlineStr">
         <is>
+          <t>SK이노베이션</t>
+        </is>
+      </c>
+      <c r="P57" s="35" t="inlineStr">
+        <is>
+          <t>화학</t>
+        </is>
+      </c>
+      <c r="Q57" s="61" t="n">
+        <v>-40</v>
+      </c>
+    </row>
+    <row r="58"/>
+    <row r="59" ht="18" customHeight="1" s="15">
+      <c r="A59" s="25" t="inlineStr">
+        <is>
+          <t>F9 보험</t>
+        </is>
+      </c>
+      <c r="E59" s="58" t="inlineStr">
+        <is>
+          <t>주간 누적 · 억원</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="59" t="inlineStr">
+        <is>
+          <t>순매수 상위</t>
+        </is>
+      </c>
+      <c r="E60" s="60" t="inlineStr">
+        <is>
+          <t>순매도 상위</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="45" t="inlineStr">
+        <is>
+          <t>순위</t>
+        </is>
+      </c>
+      <c r="B61" s="45" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="C61" s="45" t="inlineStr">
+        <is>
+          <t>섹터명</t>
+        </is>
+      </c>
+      <c r="D61" s="45" t="inlineStr">
+        <is>
+          <t>금액</t>
+        </is>
+      </c>
+      <c r="E61" s="45" t="inlineStr">
+        <is>
+          <t>순위</t>
+        </is>
+      </c>
+      <c r="F61" s="45" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="G61" s="45" t="inlineStr">
+        <is>
+          <t>섹터명</t>
+        </is>
+      </c>
+      <c r="H61" s="45" t="inlineStr">
+        <is>
+          <t>금액</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="B62" s="31" t="inlineStr">
+        <is>
+          <t>SK스퀘어</t>
+        </is>
+      </c>
+      <c r="C62" s="35" t="inlineStr">
+        <is>
+          <t>금융</t>
+        </is>
+      </c>
+      <c r="D62" s="47" t="n">
+        <v>248</v>
+      </c>
+      <c r="E62" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="F62" s="31" t="inlineStr">
+        <is>
+          <t>SK하이닉스</t>
+        </is>
+      </c>
+      <c r="G62" s="35" t="inlineStr">
+        <is>
+          <t>전기·전자</t>
+        </is>
+      </c>
+      <c r="H62" s="61" t="n">
+        <v>-311</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="30" t="n">
+        <v>2</v>
+      </c>
+      <c r="B63" s="31" t="inlineStr">
+        <is>
+          <t>삼성전자우</t>
+        </is>
+      </c>
+      <c r="C63" s="35" t="inlineStr">
+        <is>
+          <t>전기·전자</t>
+        </is>
+      </c>
+      <c r="D63" s="47" t="n">
+        <v>200</v>
+      </c>
+      <c r="E63" s="30" t="n">
+        <v>2</v>
+      </c>
+      <c r="F63" s="31" t="inlineStr">
+        <is>
+          <t>GS</t>
+        </is>
+      </c>
+      <c r="G63" s="35" t="inlineStr">
+        <is>
+          <t>금융</t>
+        </is>
+      </c>
+      <c r="H63" s="61" t="n">
+        <v>-74</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="30" t="n">
+        <v>3</v>
+      </c>
+      <c r="B64" s="31" t="inlineStr">
+        <is>
+          <t>삼성전자</t>
+        </is>
+      </c>
+      <c r="C64" s="35" t="inlineStr">
+        <is>
+          <t>전기·전자</t>
+        </is>
+      </c>
+      <c r="D64" s="47" t="n">
+        <v>130</v>
+      </c>
+      <c r="E64" s="30" t="n">
+        <v>3</v>
+      </c>
+      <c r="F64" s="31" t="inlineStr">
+        <is>
+          <t>셀트리온</t>
+        </is>
+      </c>
+      <c r="G64" s="35" t="inlineStr">
+        <is>
+          <t>제약</t>
+        </is>
+      </c>
+      <c r="H64" s="61" t="n">
+        <v>-66</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="30" t="n">
+        <v>4</v>
+      </c>
+      <c r="B65" s="31" t="inlineStr">
+        <is>
+          <t>두산에너빌리티</t>
+        </is>
+      </c>
+      <c r="C65" s="35" t="inlineStr">
+        <is>
+          <t>기계·장비</t>
+        </is>
+      </c>
+      <c r="D65" s="47" t="n">
+        <v>98</v>
+      </c>
+      <c r="E65" s="30" t="n">
+        <v>4</v>
+      </c>
+      <c r="F65" s="31" t="inlineStr">
+        <is>
+          <t>NAVER</t>
+        </is>
+      </c>
+      <c r="G65" s="35" t="inlineStr">
+        <is>
+          <t>IT 서비스</t>
+        </is>
+      </c>
+      <c r="H65" s="61" t="n">
+        <v>-61</v>
+      </c>
+    </row>
+    <row r="66" ht="31" customHeight="1" s="15">
+      <c r="A66" s="30" t="n">
+        <v>5</v>
+      </c>
+      <c r="B66" s="31" t="inlineStr">
+        <is>
+          <t>HD현대중공업</t>
+        </is>
+      </c>
+      <c r="C66" s="62" t="inlineStr">
+        <is>
+          <t>운송장비·부품</t>
+        </is>
+      </c>
+      <c r="D66" s="47" t="n">
+        <v>96</v>
+      </c>
+      <c r="E66" s="30" t="n">
+        <v>5</v>
+      </c>
+      <c r="F66" s="31" t="inlineStr">
+        <is>
+          <t>알테오젠</t>
+        </is>
+      </c>
+      <c r="G66" s="35" t="inlineStr">
+        <is>
+          <t>일반서비스</t>
+        </is>
+      </c>
+      <c r="H66" s="61" t="n">
+        <v>-60</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="30" t="n">
+        <v>6</v>
+      </c>
+      <c r="B67" s="31" t="inlineStr">
+        <is>
+          <t>두산</t>
+        </is>
+      </c>
+      <c r="C67" s="35" t="inlineStr">
+        <is>
+          <t>전기·전자</t>
+        </is>
+      </c>
+      <c r="D67" s="47" t="n">
+        <v>68</v>
+      </c>
+      <c r="E67" s="30" t="n">
+        <v>6</v>
+      </c>
+      <c r="F67" s="31" t="inlineStr">
+        <is>
+          <t>에이피알</t>
+        </is>
+      </c>
+      <c r="G67" s="35" t="inlineStr">
+        <is>
+          <t>화학</t>
+        </is>
+      </c>
+      <c r="H67" s="61" t="n">
+        <v>-57</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="30" t="n">
+        <v>7</v>
+      </c>
+      <c r="B68" s="31" t="inlineStr">
+        <is>
+          <t>현대건설</t>
+        </is>
+      </c>
+      <c r="C68" s="35" t="inlineStr">
+        <is>
+          <t>건설</t>
+        </is>
+      </c>
+      <c r="D68" s="47" t="n">
+        <v>56</v>
+      </c>
+      <c r="E68" s="30" t="n">
+        <v>7</v>
+      </c>
+      <c r="F68" s="31" t="inlineStr">
+        <is>
+          <t>HD현대일렉트릭</t>
+        </is>
+      </c>
+      <c r="G68" s="35" t="inlineStr">
+        <is>
+          <t>전기·전자</t>
+        </is>
+      </c>
+      <c r="H68" s="61" t="n">
+        <v>-57</v>
+      </c>
+    </row>
+    <row r="69" ht="31" customHeight="1" s="15">
+      <c r="A69" s="30" t="n">
+        <v>8</v>
+      </c>
+      <c r="B69" s="31" t="inlineStr">
+        <is>
+          <t>DB하이텍</t>
+        </is>
+      </c>
+      <c r="C69" s="35" t="inlineStr">
+        <is>
+          <t>전기·전자</t>
+        </is>
+      </c>
+      <c r="D69" s="47" t="n">
+        <v>44</v>
+      </c>
+      <c r="E69" s="30" t="n">
+        <v>8</v>
+      </c>
+      <c r="F69" s="31" t="inlineStr">
+        <is>
+          <t>현대모비스</t>
+        </is>
+      </c>
+      <c r="G69" s="62" t="inlineStr">
+        <is>
+          <t>운송장비·부품</t>
+        </is>
+      </c>
+      <c r="H69" s="61" t="n">
+        <v>-50</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="30" t="n">
+        <v>9</v>
+      </c>
+      <c r="B70" s="31" t="inlineStr">
+        <is>
+          <t>대우건설</t>
+        </is>
+      </c>
+      <c r="C70" s="35" t="inlineStr">
+        <is>
+          <t>건설</t>
+        </is>
+      </c>
+      <c r="D70" s="47" t="n">
+        <v>38</v>
+      </c>
+      <c r="E70" s="30" t="n">
+        <v>9</v>
+      </c>
+      <c r="F70" s="31" t="inlineStr">
+        <is>
+          <t>삼양식품</t>
+        </is>
+      </c>
+      <c r="G70" s="35" t="inlineStr">
+        <is>
+          <t>음식료·담배</t>
+        </is>
+      </c>
+      <c r="H70" s="61" t="n">
+        <v>-42</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="30" t="n">
+        <v>10</v>
+      </c>
+      <c r="B71" s="31" t="inlineStr">
+        <is>
+          <t>삼성물산</t>
+        </is>
+      </c>
+      <c r="C71" s="35" t="inlineStr">
+        <is>
+          <t>유통</t>
+        </is>
+      </c>
+      <c r="D71" s="47" t="n">
+        <v>33</v>
+      </c>
+      <c r="E71" s="30" t="n">
+        <v>10</v>
+      </c>
+      <c r="F71" s="31" t="inlineStr">
+        <is>
           <t>LG에너지솔루션</t>
         </is>
       </c>
-      <c r="P57" s="35" t="inlineStr">
+      <c r="G71" s="35" t="inlineStr">
         <is>
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="Q57" s="61" t="n">
+      <c r="H71" s="61" t="n">
         <v>-42</v>
       </c>
     </row>
-    <row r="58"/>
-    <row r="59" ht="31" customHeight="1" s="15">
-      <c r="A59" s="63" t="inlineStr">
-        <is>
-          <t>외인·기관 동시 등재 종목=종목명 굵게(동반 매수/매도) · netbuy_rank 일별 아카이브 합산 — 상위 30 리스트 등재일만 반영되는 근사치 · 금융투자=증권, 투신(사모)=투자신탁+사모펀드 (확정 병합분) · 외인+기관=합산 카드와 동일</t>
+    <row r="72"/>
+    <row r="73" ht="31" customHeight="1" s="15">
+      <c r="A73" s="63" t="inlineStr">
+        <is>
+          <t>외인·기관 동시 등재 종목=종목명 굵게(동반 매수/매도) · netbuy_rank 일별 아카이브 합산 — 상위 30 리스트 등재일만 반영되는 근사치 · 금융투자=증권, 투신(사모)=투자신탁+사모펀드, 기타법인=일반법인(자사주 매입 등) (확정 병합분) · 외인+기관=합산 카드와 동일</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="35">
+  <mergeCells count="39">
     <mergeCell ref="A17:D17"/>
     <mergeCell ref="E45:H45"/>
     <mergeCell ref="O1:Q1"/>
@@ -9415,7 +9822,7 @@
     <mergeCell ref="J31:M31"/>
     <mergeCell ref="A4:D4"/>
     <mergeCell ref="J3:M3"/>
-    <mergeCell ref="A59:Q59"/>
+    <mergeCell ref="A73:Q73"/>
     <mergeCell ref="J46:M46"/>
     <mergeCell ref="E32:H32"/>
     <mergeCell ref="J18:M18"/>
@@ -9425,7 +9832,9 @@
     <mergeCell ref="E3:H3"/>
     <mergeCell ref="J17:M17"/>
     <mergeCell ref="N4:Q4"/>
+    <mergeCell ref="A59:D59"/>
     <mergeCell ref="N32:Q32"/>
+    <mergeCell ref="A60:D60"/>
     <mergeCell ref="A45:D45"/>
     <mergeCell ref="E17:H17"/>
     <mergeCell ref="A1:M1"/>
@@ -9436,11 +9845,13 @@
     <mergeCell ref="N18:Q18"/>
     <mergeCell ref="J45:M45"/>
     <mergeCell ref="A18:D18"/>
+    <mergeCell ref="E60:H60"/>
     <mergeCell ref="E31:H31"/>
     <mergeCell ref="N17:Q17"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="J4:M4"/>
     <mergeCell ref="E46:H46"/>
+    <mergeCell ref="E59:H59"/>
     <mergeCell ref="J32:M32"/>
     <mergeCell ref="A32:D32"/>
   </mergeCells>
@@ -9455,7 +9866,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:P16"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4.5" customWidth="1" style="15" min="1" max="1"/>
     <col width="16" customWidth="1" style="15" min="2" max="2"/>
@@ -10161,8 +10572,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N31"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <dimension ref="A1:O31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20.5" customWidth="1" style="15" min="1" max="1"/>
     <col width="8.199999999999999" customWidth="1" style="15" min="2" max="2"/>
@@ -10177,7 +10588,8 @@
     <col width="9.5" customWidth="1" style="15" min="11" max="11"/>
     <col width="9.5" customWidth="1" style="15" min="12" max="12"/>
     <col width="9.5" customWidth="1" style="15" min="13" max="13"/>
-    <col width="11.5" customWidth="1" style="15" min="14" max="14"/>
+    <col width="9.5" customWidth="1" style="15" min="14" max="14"/>
+    <col width="11.5" customWidth="1" style="15" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1" ht="20.25" customHeight="1" s="15">
@@ -10225,6 +10637,7 @@
       </c>
       <c r="M3" s="3" t="inlineStr"/>
       <c r="N3" s="3" t="inlineStr"/>
+      <c r="O3" s="3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="45" t="inlineStr">
@@ -10284,15 +10697,20 @@
       </c>
       <c r="L4" s="45" t="inlineStr">
         <is>
+          <t>기타법인</t>
+        </is>
+      </c>
+      <c r="M4" s="45" t="inlineStr">
+        <is>
           <t>보험</t>
         </is>
       </c>
-      <c r="M4" s="45" t="inlineStr">
+      <c r="N4" s="45" t="inlineStr">
         <is>
           <t>개인</t>
         </is>
       </c>
-      <c r="N4" s="45" t="inlineStr">
+      <c r="O4" s="45" t="inlineStr">
         <is>
           <t>신호</t>
         </is>
@@ -10334,13 +10752,14 @@
       <c r="K5" s="69" t="n">
         <v>369</v>
       </c>
-      <c r="L5" s="69" t="n">
+      <c r="L5" s="70" t="inlineStr"/>
+      <c r="M5" s="69" t="n">
         <v>85</v>
       </c>
-      <c r="M5" s="68" t="n">
+      <c r="N5" s="68" t="n">
         <v>-2741</v>
       </c>
-      <c r="N5" s="59" t="inlineStr">
+      <c r="O5" s="59" t="inlineStr">
         <is>
           <t>동반강세</t>
         </is>
@@ -10355,7 +10774,7 @@
       <c r="B6" s="67" t="n">
         <v>19.08</v>
       </c>
-      <c r="C6" s="70" t="n">
+      <c r="C6" s="71" t="n">
         <v>-7.16</v>
       </c>
       <c r="D6" s="67" t="n">
@@ -10382,13 +10801,14 @@
       <c r="K6" s="69" t="n">
         <v>1078</v>
       </c>
-      <c r="L6" s="69" t="n">
+      <c r="L6" s="70" t="inlineStr"/>
+      <c r="M6" s="69" t="n">
         <v>153</v>
       </c>
-      <c r="M6" s="68" t="n">
+      <c r="N6" s="68" t="n">
         <v>-2644</v>
       </c>
-      <c r="N6" s="59" t="inlineStr">
+      <c r="O6" s="59" t="inlineStr">
         <is>
           <t>동반강세</t>
         </is>
@@ -10430,13 +10850,14 @@
       <c r="K7" s="69" t="n">
         <v>532</v>
       </c>
-      <c r="L7" s="69" t="n">
+      <c r="L7" s="70" t="inlineStr"/>
+      <c r="M7" s="69" t="n">
         <v>27</v>
       </c>
-      <c r="M7" s="68" t="n">
+      <c r="N7" s="68" t="n">
         <v>-895</v>
       </c>
-      <c r="N7" s="59" t="inlineStr">
+      <c r="O7" s="59" t="inlineStr">
         <is>
           <t>동반강세</t>
         </is>
@@ -10451,7 +10872,7 @@
       <c r="B8" s="67" t="n">
         <v>113.57</v>
       </c>
-      <c r="C8" s="70" t="n">
+      <c r="C8" s="71" t="n">
         <v>-13.79</v>
       </c>
       <c r="D8" s="67" t="n">
@@ -10478,13 +10899,14 @@
       <c r="K8" s="68" t="n">
         <v>-1123</v>
       </c>
-      <c r="L8" s="68" t="n">
+      <c r="L8" s="70" t="inlineStr"/>
+      <c r="M8" s="68" t="n">
         <v>-7</v>
       </c>
-      <c r="M8" s="68" t="n">
+      <c r="N8" s="68" t="n">
         <v>-92685</v>
       </c>
-      <c r="N8" s="30" t="inlineStr"/>
+      <c r="O8" s="30" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="31" t="inlineStr">
@@ -10495,7 +10917,7 @@
       <c r="B9" s="67" t="n">
         <v>73.06</v>
       </c>
-      <c r="C9" s="70" t="n">
+      <c r="C9" s="71" t="n">
         <v>-13.01</v>
       </c>
       <c r="D9" s="67" t="n">
@@ -10522,13 +10944,14 @@
       <c r="K9" s="68" t="n">
         <v>-2238</v>
       </c>
-      <c r="L9" s="68" t="n">
+      <c r="L9" s="70" t="inlineStr"/>
+      <c r="M9" s="68" t="n">
         <v>-126</v>
       </c>
-      <c r="M9" s="68" t="n">
+      <c r="N9" s="68" t="n">
         <v>-90654</v>
       </c>
-      <c r="N9" s="30" t="inlineStr"/>
+      <c r="O9" s="30" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="31" t="inlineStr">
@@ -10536,13 +10959,13 @@
           <t>전기·가스</t>
         </is>
       </c>
-      <c r="B10" s="70" t="n">
+      <c r="B10" s="71" t="n">
         <v>-23.14</v>
       </c>
-      <c r="C10" s="70" t="n">
+      <c r="C10" s="71" t="n">
         <v>-4.84</v>
       </c>
-      <c r="D10" s="70" t="n">
+      <c r="D10" s="71" t="n">
         <v>-3.89</v>
       </c>
       <c r="E10" s="67" t="n">
@@ -10566,13 +10989,14 @@
       <c r="K10" s="69" t="n">
         <v>149</v>
       </c>
-      <c r="L10" s="69" t="n">
+      <c r="L10" s="70" t="inlineStr"/>
+      <c r="M10" s="69" t="n">
         <v>18</v>
       </c>
-      <c r="M10" s="68" t="n">
+      <c r="N10" s="68" t="n">
         <v>-194</v>
       </c>
-      <c r="N10" s="71" t="inlineStr">
+      <c r="O10" s="72" t="inlineStr">
         <is>
           <t>수급유입</t>
         </is>
@@ -10587,7 +11011,7 @@
       <c r="B11" s="67" t="n">
         <v>64.67</v>
       </c>
-      <c r="C11" s="70" t="n">
+      <c r="C11" s="71" t="n">
         <v>-4.1</v>
       </c>
       <c r="D11" s="67" t="n">
@@ -10614,13 +11038,14 @@
       <c r="K11" s="69" t="n">
         <v>686</v>
       </c>
-      <c r="L11" s="68" t="n">
+      <c r="L11" s="70" t="inlineStr"/>
+      <c r="M11" s="68" t="n">
         <v>-34</v>
       </c>
-      <c r="M11" s="68" t="n">
+      <c r="N11" s="68" t="n">
         <v>-576</v>
       </c>
-      <c r="N11" s="59" t="inlineStr">
+      <c r="O11" s="59" t="inlineStr">
         <is>
           <t>동반강세</t>
         </is>
@@ -10635,7 +11060,7 @@
       <c r="B12" s="67" t="n">
         <v>46.4</v>
       </c>
-      <c r="C12" s="70" t="n">
+      <c r="C12" s="71" t="n">
         <v>-1.5</v>
       </c>
       <c r="D12" s="67" t="n">
@@ -10662,13 +11087,14 @@
       <c r="K12" s="69" t="n">
         <v>1170</v>
       </c>
-      <c r="L12" s="68" t="n">
+      <c r="L12" s="70" t="inlineStr"/>
+      <c r="M12" s="68" t="n">
         <v>-39</v>
       </c>
-      <c r="M12" s="68" t="n">
+      <c r="N12" s="68" t="n">
         <v>-6022</v>
       </c>
-      <c r="N12" s="59" t="inlineStr">
+      <c r="O12" s="59" t="inlineStr">
         <is>
           <t>동반강세</t>
         </is>
@@ -10683,10 +11109,10 @@
       <c r="B13" s="67" t="n">
         <v>1.91</v>
       </c>
-      <c r="C13" s="70" t="n">
+      <c r="C13" s="71" t="n">
         <v>-22.47</v>
       </c>
-      <c r="D13" s="70" t="n">
+      <c r="D13" s="71" t="n">
         <v>-5.88</v>
       </c>
       <c r="E13" s="67" t="n">
@@ -10710,13 +11136,14 @@
       <c r="K13" s="68" t="n">
         <v>-1437</v>
       </c>
-      <c r="L13" s="68" t="n">
+      <c r="L13" s="70" t="inlineStr"/>
+      <c r="M13" s="68" t="n">
         <v>-67</v>
       </c>
-      <c r="M13" s="69" t="n">
+      <c r="N13" s="69" t="n">
         <v>1322</v>
       </c>
-      <c r="N13" s="30" t="inlineStr"/>
+      <c r="O13" s="30" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="31" t="inlineStr">
@@ -10727,7 +11154,7 @@
       <c r="B14" s="67" t="n">
         <v>10.33</v>
       </c>
-      <c r="C14" s="70" t="n">
+      <c r="C14" s="71" t="n">
         <v>-7.32</v>
       </c>
       <c r="D14" s="67" t="n">
@@ -10754,13 +11181,14 @@
       <c r="K14" s="69" t="n">
         <v>93</v>
       </c>
-      <c r="L14" s="69" t="n">
+      <c r="L14" s="70" t="inlineStr"/>
+      <c r="M14" s="69" t="n">
         <v>13</v>
       </c>
-      <c r="M14" s="69" t="n">
+      <c r="N14" s="69" t="n">
         <v>72</v>
       </c>
-      <c r="N14" s="72" t="inlineStr">
+      <c r="O14" s="73" t="inlineStr">
         <is>
           <t>수급이탈</t>
         </is>
@@ -10775,7 +11203,7 @@
       <c r="B15" s="67" t="n">
         <v>30.09</v>
       </c>
-      <c r="C15" s="70" t="n">
+      <c r="C15" s="71" t="n">
         <v>-13.16</v>
       </c>
       <c r="D15" s="67" t="n">
@@ -10802,13 +11230,14 @@
       <c r="K15" s="68" t="n">
         <v>-76</v>
       </c>
-      <c r="L15" s="69" t="n">
+      <c r="L15" s="70" t="inlineStr"/>
+      <c r="M15" s="69" t="n">
         <v>14</v>
       </c>
-      <c r="M15" s="68" t="n">
+      <c r="N15" s="68" t="n">
         <v>-511</v>
       </c>
-      <c r="N15" s="30" t="inlineStr"/>
+      <c r="O15" s="30" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="31" t="inlineStr">
@@ -10816,13 +11245,13 @@
           <t>부동산</t>
         </is>
       </c>
-      <c r="B16" s="70" t="n">
+      <c r="B16" s="71" t="n">
         <v>-9.380000000000001</v>
       </c>
       <c r="C16" s="67" t="n">
         <v>0.67</v>
       </c>
-      <c r="D16" s="70" t="n">
+      <c r="D16" s="71" t="n">
         <v>-0.98</v>
       </c>
       <c r="E16" s="67" t="n">
@@ -10846,13 +11275,14 @@
       <c r="K16" s="69" t="n">
         <v>70</v>
       </c>
-      <c r="L16" s="68" t="n">
+      <c r="L16" s="70" t="inlineStr"/>
+      <c r="M16" s="68" t="n">
         <v>-9</v>
       </c>
-      <c r="M16" s="68" t="n">
+      <c r="N16" s="68" t="n">
         <v>-88</v>
       </c>
-      <c r="N16" s="30" t="inlineStr"/>
+      <c r="O16" s="30" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="31" t="inlineStr">
@@ -10863,13 +11293,13 @@
       <c r="B17" s="67" t="n">
         <v>5.71</v>
       </c>
-      <c r="C17" s="70" t="n">
+      <c r="C17" s="71" t="n">
         <v>-3.92</v>
       </c>
-      <c r="D17" s="70" t="n">
+      <c r="D17" s="71" t="n">
         <v>-1.73</v>
       </c>
-      <c r="E17" s="70" t="n">
+      <c r="E17" s="71" t="n">
         <v>-0.34</v>
       </c>
       <c r="F17" s="68" t="n">
@@ -10890,13 +11320,14 @@
       <c r="K17" s="68" t="n">
         <v>-45</v>
       </c>
-      <c r="L17" s="69" t="n">
+      <c r="L17" s="70" t="inlineStr"/>
+      <c r="M17" s="69" t="n">
         <v>7</v>
       </c>
-      <c r="M17" s="69" t="n">
+      <c r="N17" s="69" t="n">
         <v>211</v>
       </c>
-      <c r="N17" s="60" t="inlineStr">
+      <c r="O17" s="60" t="inlineStr">
         <is>
           <t>동반약세</t>
         </is>
@@ -10911,13 +11342,13 @@
       <c r="B18" s="67" t="n">
         <v>18.17</v>
       </c>
-      <c r="C18" s="70" t="n">
+      <c r="C18" s="71" t="n">
         <v>-23.47</v>
       </c>
-      <c r="D18" s="70" t="n">
+      <c r="D18" s="71" t="n">
         <v>-5.25</v>
       </c>
-      <c r="E18" s="70" t="n">
+      <c r="E18" s="71" t="n">
         <v>-0.82</v>
       </c>
       <c r="F18" s="69" t="n">
@@ -10938,13 +11369,14 @@
       <c r="K18" s="68" t="n">
         <v>-297</v>
       </c>
-      <c r="L18" s="68" t="n">
+      <c r="L18" s="70" t="inlineStr"/>
+      <c r="M18" s="68" t="n">
         <v>-32</v>
       </c>
-      <c r="M18" s="68" t="n">
+      <c r="N18" s="68" t="n">
         <v>-84</v>
       </c>
-      <c r="N18" s="30" t="inlineStr"/>
+      <c r="O18" s="30" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="31" t="inlineStr">
@@ -10961,7 +11393,7 @@
       <c r="D19" s="67" t="n">
         <v>2.27</v>
       </c>
-      <c r="E19" s="70" t="n">
+      <c r="E19" s="71" t="n">
         <v>-0.91</v>
       </c>
       <c r="F19" s="69" t="n">
@@ -10982,13 +11414,14 @@
       <c r="K19" s="69" t="n">
         <v>236</v>
       </c>
-      <c r="L19" s="68" t="n">
+      <c r="L19" s="70" t="inlineStr"/>
+      <c r="M19" s="68" t="n">
         <v>-39</v>
       </c>
-      <c r="M19" s="69" t="n">
+      <c r="N19" s="69" t="n">
         <v>212</v>
       </c>
-      <c r="N19" s="30" t="inlineStr"/>
+      <c r="O19" s="30" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="31" t="inlineStr">
@@ -10996,7 +11429,7 @@
           <t>비금속</t>
         </is>
       </c>
-      <c r="B20" s="70" t="n">
+      <c r="B20" s="71" t="n">
         <v>-11.91</v>
       </c>
       <c r="C20" s="67" t="n">
@@ -11005,7 +11438,7 @@
       <c r="D20" s="67" t="n">
         <v>0.62</v>
       </c>
-      <c r="E20" s="70" t="n">
+      <c r="E20" s="71" t="n">
         <v>-0.92</v>
       </c>
       <c r="F20" s="68" t="n">
@@ -11026,13 +11459,14 @@
       <c r="K20" s="68" t="n">
         <v>-20</v>
       </c>
-      <c r="L20" s="73" t="n">
+      <c r="L20" s="70" t="inlineStr"/>
+      <c r="M20" s="70" t="n">
         <v>0</v>
       </c>
-      <c r="M20" s="69" t="n">
+      <c r="N20" s="69" t="n">
         <v>55</v>
       </c>
-      <c r="N20" s="30" t="inlineStr"/>
+      <c r="O20" s="30" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="31" t="inlineStr">
@@ -11049,7 +11483,7 @@
       <c r="D21" s="67" t="n">
         <v>1.34</v>
       </c>
-      <c r="E21" s="70" t="n">
+      <c r="E21" s="71" t="n">
         <v>-0.92</v>
       </c>
       <c r="F21" s="69" t="n">
@@ -11070,13 +11504,14 @@
       <c r="K21" s="68" t="n">
         <v>-8</v>
       </c>
-      <c r="L21" s="69" t="n">
+      <c r="L21" s="70" t="inlineStr"/>
+      <c r="M21" s="69" t="n">
         <v>3</v>
       </c>
-      <c r="M21" s="68" t="n">
+      <c r="N21" s="68" t="n">
         <v>-735</v>
       </c>
-      <c r="N21" s="59" t="inlineStr">
+      <c r="O21" s="59" t="inlineStr">
         <is>
           <t>동반강세</t>
         </is>
@@ -11088,16 +11523,16 @@
           <t>섬유·의류</t>
         </is>
       </c>
-      <c r="B22" s="70" t="n">
+      <c r="B22" s="71" t="n">
         <v>-7.71</v>
       </c>
-      <c r="C22" s="70" t="n">
+      <c r="C22" s="71" t="n">
         <v>-9.56</v>
       </c>
-      <c r="D22" s="70" t="n">
+      <c r="D22" s="71" t="n">
         <v>-2.27</v>
       </c>
-      <c r="E22" s="70" t="n">
+      <c r="E22" s="71" t="n">
         <v>-1.18</v>
       </c>
       <c r="F22" s="68" t="n">
@@ -11118,13 +11553,14 @@
       <c r="K22" s="69" t="n">
         <v>17</v>
       </c>
-      <c r="L22" s="68" t="n">
+      <c r="L22" s="70" t="inlineStr"/>
+      <c r="M22" s="68" t="n">
         <v>-3</v>
       </c>
-      <c r="M22" s="69" t="n">
+      <c r="N22" s="69" t="n">
         <v>25</v>
       </c>
-      <c r="N22" s="60" t="inlineStr">
+      <c r="O22" s="60" t="inlineStr">
         <is>
           <t>동반약세</t>
         </is>
@@ -11139,13 +11575,13 @@
       <c r="B23" s="67" t="n">
         <v>27.78</v>
       </c>
-      <c r="C23" s="70" t="n">
+      <c r="C23" s="71" t="n">
         <v>-9.15</v>
       </c>
       <c r="D23" s="67" t="n">
         <v>1.92</v>
       </c>
-      <c r="E23" s="70" t="n">
+      <c r="E23" s="71" t="n">
         <v>-1.7</v>
       </c>
       <c r="F23" s="69" t="n">
@@ -11166,13 +11602,14 @@
       <c r="K23" s="68" t="n">
         <v>-52</v>
       </c>
-      <c r="L23" s="68" t="n">
+      <c r="L23" s="70" t="inlineStr"/>
+      <c r="M23" s="68" t="n">
         <v>-43</v>
       </c>
-      <c r="M23" s="69" t="n">
+      <c r="N23" s="69" t="n">
         <v>6</v>
       </c>
-      <c r="N23" s="30" t="inlineStr"/>
+      <c r="O23" s="30" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="31" t="inlineStr">
@@ -11180,7 +11617,7 @@
           <t>종이·목재</t>
         </is>
       </c>
-      <c r="B24" s="70" t="n">
+      <c r="B24" s="71" t="n">
         <v>-18.75</v>
       </c>
       <c r="C24" s="67" t="n">
@@ -11189,7 +11626,7 @@
       <c r="D24" s="67" t="n">
         <v>0.75</v>
       </c>
-      <c r="E24" s="70" t="n">
+      <c r="E24" s="71" t="n">
         <v>-1.83</v>
       </c>
       <c r="F24" s="68" t="n">
@@ -11207,16 +11644,17 @@
       <c r="J24" s="69" t="n">
         <v>2</v>
       </c>
-      <c r="K24" s="73" t="n">
+      <c r="K24" s="70" t="n">
         <v>0</v>
       </c>
-      <c r="L24" s="73" t="n">
+      <c r="L24" s="70" t="inlineStr"/>
+      <c r="M24" s="70" t="n">
         <v>0</v>
       </c>
-      <c r="M24" s="68" t="n">
+      <c r="N24" s="68" t="n">
         <v>-6</v>
       </c>
-      <c r="N24" s="30" t="inlineStr"/>
+      <c r="O24" s="30" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="31" t="inlineStr">
@@ -11224,16 +11662,16 @@
           <t>오락·문화</t>
         </is>
       </c>
-      <c r="B25" s="70" t="n">
+      <c r="B25" s="71" t="n">
         <v>-41.38</v>
       </c>
-      <c r="C25" s="70" t="n">
+      <c r="C25" s="71" t="n">
         <v>-16.46</v>
       </c>
-      <c r="D25" s="70" t="n">
+      <c r="D25" s="71" t="n">
         <v>-2.27</v>
       </c>
-      <c r="E25" s="70" t="n">
+      <c r="E25" s="71" t="n">
         <v>-1.83</v>
       </c>
       <c r="F25" s="68" t="n">
@@ -11254,13 +11692,14 @@
       <c r="K25" s="68" t="n">
         <v>-63</v>
       </c>
-      <c r="L25" s="68" t="n">
+      <c r="L25" s="70" t="inlineStr"/>
+      <c r="M25" s="68" t="n">
         <v>-13</v>
       </c>
-      <c r="M25" s="69" t="n">
+      <c r="N25" s="69" t="n">
         <v>245</v>
       </c>
-      <c r="N25" s="60" t="inlineStr">
+      <c r="O25" s="60" t="inlineStr">
         <is>
           <t>동반약세</t>
         </is>
@@ -11272,16 +11711,16 @@
           <t>제약</t>
         </is>
       </c>
-      <c r="B26" s="70" t="n">
+      <c r="B26" s="71" t="n">
         <v>-13.95</v>
       </c>
       <c r="C26" s="67" t="n">
         <v>7.05</v>
       </c>
-      <c r="D26" s="70" t="n">
+      <c r="D26" s="71" t="n">
         <v>-11.15</v>
       </c>
-      <c r="E26" s="70" t="n">
+      <c r="E26" s="71" t="n">
         <v>-3.09</v>
       </c>
       <c r="F26" s="69" t="n">
@@ -11302,13 +11741,14 @@
       <c r="K26" s="68" t="n">
         <v>-901</v>
       </c>
-      <c r="L26" s="68" t="n">
+      <c r="L26" s="70" t="inlineStr"/>
+      <c r="M26" s="68" t="n">
         <v>-120</v>
       </c>
-      <c r="M26" s="69" t="n">
+      <c r="N26" s="69" t="n">
         <v>1302</v>
       </c>
-      <c r="N26" s="60" t="inlineStr">
+      <c r="O26" s="60" t="inlineStr">
         <is>
           <t>동반약세</t>
         </is>
@@ -11323,13 +11763,13 @@
       <c r="B27" s="67" t="n">
         <v>6.05</v>
       </c>
-      <c r="C27" s="70" t="n">
+      <c r="C27" s="71" t="n">
         <v>-1.31</v>
       </c>
-      <c r="D27" s="70" t="n">
+      <c r="D27" s="71" t="n">
         <v>-2.23</v>
       </c>
-      <c r="E27" s="70" t="n">
+      <c r="E27" s="71" t="n">
         <v>-3.31</v>
       </c>
       <c r="F27" s="69" t="n">
@@ -11350,13 +11790,14 @@
       <c r="K27" s="68" t="n">
         <v>-137</v>
       </c>
-      <c r="L27" s="68" t="n">
+      <c r="L27" s="70" t="inlineStr"/>
+      <c r="M27" s="68" t="n">
         <v>-63</v>
       </c>
-      <c r="M27" s="69" t="n">
+      <c r="N27" s="69" t="n">
         <v>1489</v>
       </c>
-      <c r="N27" s="60" t="inlineStr">
+      <c r="O27" s="60" t="inlineStr">
         <is>
           <t>동반약세</t>
         </is>
@@ -11368,16 +11809,16 @@
           <t>IT 서비스</t>
         </is>
       </c>
-      <c r="B28" s="70" t="n">
+      <c r="B28" s="71" t="n">
         <v>-10.86</v>
       </c>
-      <c r="C28" s="70" t="n">
+      <c r="C28" s="71" t="n">
         <v>-13.95</v>
       </c>
-      <c r="D28" s="70" t="n">
+      <c r="D28" s="71" t="n">
         <v>-7.97</v>
       </c>
-      <c r="E28" s="70" t="n">
+      <c r="E28" s="71" t="n">
         <v>-3.84</v>
       </c>
       <c r="F28" s="69" t="n">
@@ -11398,13 +11839,14 @@
       <c r="K28" s="68" t="n">
         <v>-1320</v>
       </c>
-      <c r="L28" s="68" t="n">
+      <c r="L28" s="70" t="inlineStr"/>
+      <c r="M28" s="68" t="n">
         <v>-159</v>
       </c>
-      <c r="M28" s="69" t="n">
+      <c r="N28" s="69" t="n">
         <v>2501</v>
       </c>
-      <c r="N28" s="60" t="inlineStr">
+      <c r="O28" s="60" t="inlineStr">
         <is>
           <t>동반약세</t>
         </is>
@@ -11426,12 +11868,12 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:N28"/>
+  <autoFilter ref="A4:O28"/>
   <mergeCells count="4">
-    <mergeCell ref="L1:N1"/>
     <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A31:N31"/>
-    <mergeCell ref="A30:N30"/>
+    <mergeCell ref="L1:O1"/>
+    <mergeCell ref="A31:O31"/>
+    <mergeCell ref="A30:O30"/>
   </mergeCells>
   <conditionalFormatting sqref="B5:B28">
     <cfRule type="dataBar" priority="1">
@@ -11442,7 +11884,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{36257F91-FA94-44F5-A4E4-61AAB128A267}</x14:id>
+          <x14:id>{191E0178-37F9-4C63-BD99-25281DAA95C2}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11456,7 +11898,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{B53697D0-3365-4C7F-BF7A-10E96B748440}</x14:id>
+          <x14:id>{4AA5E0A4-6A17-464F-AD70-996121E736CD}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11470,7 +11912,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ECAF86A2-A0A2-432E-8B59-31366CE3247E}</x14:id>
+          <x14:id>{915C94F0-3E31-4A13-81F3-006F59E3ACE2}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11484,7 +11926,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{5F12E336-8C8B-44DC-A076-8E6A1C37E5AC}</x14:id>
+          <x14:id>{CA5BFB5F-2CF0-44E8-81E6-E2504B429E59}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11494,7 +11936,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{36257F91-FA94-44F5-A4E4-61AAB128A267}">
+          <x14:cfRule type="dataBar" id="{191E0178-37F9-4C63-BD99-25281DAA95C2}">
             <x14:dataBar minLength="0" maxLength="100" border="1" axisPosition="automatic" negativeBarColorSameAsPositive="0" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -11507,7 +11949,7 @@
           <xm:sqref>B5:B28</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{B53697D0-3365-4C7F-BF7A-10E96B748440}">
+          <x14:cfRule type="dataBar" id="{4AA5E0A4-6A17-464F-AD70-996121E736CD}">
             <x14:dataBar minLength="0" maxLength="100" border="1" axisPosition="automatic" negativeBarColorSameAsPositive="0" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -11520,7 +11962,7 @@
           <xm:sqref>C5:C28</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{ECAF86A2-A0A2-432E-8B59-31366CE3247E}">
+          <x14:cfRule type="dataBar" id="{915C94F0-3E31-4A13-81F3-006F59E3ACE2}">
             <x14:dataBar minLength="0" maxLength="100" border="1" axisPosition="automatic" negativeBarColorSameAsPositive="0" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -11533,7 +11975,7 @@
           <xm:sqref>D5:D28</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{5F12E336-8C8B-44DC-A076-8E6A1C37E5AC}">
+          <x14:cfRule type="dataBar" id="{CA5BFB5F-2CF0-44E8-81E6-E2504B429E59}">
             <x14:dataBar minLength="0" maxLength="100" border="1" axisPosition="automatic" negativeBarColorSameAsPositive="0" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
